--- a/outputs/daily/hr_rankings_2026-08-16_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-16_remaining.xlsx
@@ -1045,7 +1045,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>53</v>
+        <v>53.9</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1091,7 +1091,7 @@
         <v>43.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1101,37 +1101,29 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>not found on RotoWire</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1864,7 +1856,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Julio Rodriguez</t>
+          <t>Julio Rodríguez</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1889,7 +1881,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1908,7 +1900,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>44.7</v>
+        <v>46.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1922,7 +1914,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1935,7 +1927,7 @@
         <v>43.1</v>
       </c>
       <c r="S6" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
@@ -1945,39 +1937,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2173,7 +2161,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2192,7 +2180,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>44.6</v>
+        <v>45.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2206,7 +2194,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2219,7 +2207,7 @@
         <v>43.1</v>
       </c>
       <c r="S7" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
@@ -2229,39 +2217,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2427,12 +2411,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>801126</t>
+          <t>663728</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brock Rodden</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2457,7 +2441,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2476,7 +2460,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.8</v>
+        <v>45.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2490,11 +2474,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>57.3</v>
+        <v>54</v>
       </c>
       <c r="Q8" t="n">
         <v>21.2</v>
@@ -2503,52 +2487,48 @@
         <v>43.1</v>
       </c>
       <c r="S8" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T8" t="n">
         <v>75</v>
       </c>
       <c r="U8" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -2560,17 +2540,17 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2580,7 +2560,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 2 games: 2/8, 0 HR</t>
+          <t>Last 7 games: 2/23, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2595,67 +2575,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>98.2126</t>
+          <t>100.7149</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.4161</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.2236</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>75.06</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>53.38</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1971</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2711,24 +2691,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>665161</t>
+          <t>801126</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jeremy Peña</t>
+          <t>Brock Rodden</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -2741,17 +2721,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2760,7 +2740,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>43.7</v>
+        <v>44.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2774,26 +2754,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>29.3</v>
+        <v>57.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>21.2</v>
       </c>
       <c r="R9" t="n">
         <v>43.1</v>
       </c>
       <c r="S9" t="n">
-        <v>93.2</v>
+        <v>44.8</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>19.5</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2807,7 +2787,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2828,7 +2808,7 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -2840,17 +2820,17 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2860,112 +2840,112 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/31, 0 HR</t>
+          <t>Last 2 games: 2/8, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>88.48</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>99.8917</t>
+          <t>98.2126</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4222</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1438</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>72.23</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1793</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -2991,12 +2971,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>670623</t>
+          <t>665161</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Isaac Paredes</t>
+          <t>Jeremy Peña</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3021,7 +3001,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3040,7 +3020,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>43.2</v>
+        <v>43.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3058,7 +3038,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>18.7</v>
+        <v>29.3</v>
       </c>
       <c r="Q10" t="n">
         <v>41.2</v>
@@ -3067,13 +3047,13 @@
         <v>43.1</v>
       </c>
       <c r="S10" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>53.9</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3087,7 +3067,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -3125,22 +3105,22 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Contact streak: 10/28 over last 7 games</t>
+          <t>Last 7 games: 4/31, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -3155,67 +3135,67 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>86.49</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>96.9468</t>
+          <t>99.8917</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.3772</t>
+          <t>0.4222</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1327</t>
+          <t>0.1438</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3214</t>
+          <t>0.3333</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>67.81</t>
+          <t>72.23</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>14.27</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>52.28</t>
+          <t>45.92</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>30.87</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1767</t>
+          <t>0.1793</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -3271,12 +3251,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>663728</t>
+          <t>647304</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Josh Naylor</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3301,7 +3281,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3320,7 +3300,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>42.8</v>
+        <v>43.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3334,62 +3314,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>54</v>
+        <v>24.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>21.2</v>
+        <v>22.3</v>
       </c>
       <c r="R11" t="n">
         <v>43.1</v>
       </c>
       <c r="S11" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>78.7</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3409,97 +3385,97 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/23, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.7149</t>
+          <t>99.1945</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4161</t>
+          <t>0.4068</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2236</t>
+          <t>0.1345</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>75.06</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>53.38</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1971</t>
+          <t>0.1257</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -3555,24 +3531,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>702284</t>
+          <t>670623</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cole Young</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -3585,17 +3561,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3604,7 +3580,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>42.5</v>
+        <v>43.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3618,62 +3594,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>24.9</v>
+        <v>18.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>22.3</v>
+        <v>41.2</v>
       </c>
       <c r="R12" t="n">
         <v>43.1</v>
       </c>
       <c r="S12" t="n">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>37.8</v>
+        <v>53.9</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3693,7 +3665,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
@@ -3708,12 +3680,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 1 HR</t>
+          <t>Contact streak: 10/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3723,97 +3695,97 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>36.63</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>88.51</t>
+          <t>86.49</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>99.0446</t>
+          <t>96.9468</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3935</t>
+          <t>0.3772</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1345</t>
+          <t>0.1327</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3166</t>
+          <t>0.3214</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>71.51</t>
+          <t>67.81</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>7.64</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>52.28</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27.22</t>
+          <t>30.87</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1767</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -3839,24 +3811,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>647304</t>
+          <t>514888</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Josh Naylor</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -3869,17 +3841,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3888,7 +3860,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>41.1</v>
+        <v>39.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3902,62 +3874,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>24.7</v>
+        <v>14.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>22.3</v>
+        <v>41.2</v>
       </c>
       <c r="R13" t="n">
         <v>43.1</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>78.7</v>
+        <v>21.1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3977,27 +3945,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/23, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -4007,97 +3975,97 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>85.24</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>99.1945</t>
+          <t>96.9722</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4068</t>
+          <t>0.3483</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1345</t>
+          <t>0.1197</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.2839</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>69.07</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1257</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -4123,24 +4091,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>514888</t>
+          <t>702284</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Cole Young</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -4153,17 +4121,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4172,7 +4140,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4186,26 +4154,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>14.3</v>
+        <v>24.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>22.3</v>
       </c>
       <c r="R14" t="n">
         <v>43.1</v>
       </c>
       <c r="S14" t="n">
-        <v>94.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>21.1</v>
+        <v>37.8</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4219,7 +4187,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4257,27 +4225,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 0 HR</t>
+          <t>Last 7 games: 7/28, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4287,97 +4255,97 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>36.63</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>85.24</t>
+          <t>88.51</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>96.9722</t>
+          <t>99.0446</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3483</t>
+          <t>0.3935</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1197</t>
+          <t>0.1345</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2839</t>
+          <t>0.3166</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>71.51</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>21.44</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>41.63</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>27.22</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -4403,12 +4371,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>621493</t>
+          <t>680977</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Brendan Donovan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4452,7 +4420,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>39.8</v>
+        <v>38.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4466,11 +4434,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>32.2</v>
+        <v>15.9</v>
       </c>
       <c r="Q15" t="n">
         <v>22.3</v>
@@ -4479,49 +4447,45 @@
         <v>43.1</v>
       </c>
       <c r="S15" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>7.9</v>
+        <v>20.9</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4541,12 +4505,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4556,12 +4520,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/29, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4571,67 +4535,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>31.87</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>89.26</t>
+          <t>86.62</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>99.4443</t>
+          <t>97.0553</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3975</t>
+          <t>0.3741</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1546</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3379</t>
+          <t>0.3194</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>68.67</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>22.79</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -5247,12 +5211,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>680977</t>
+          <t>642215</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brendan Donovan</t>
+          <t>Weston Wilson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5277,7 +5241,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5296,7 +5260,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>33.7</v>
+        <v>32.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5310,11 +5274,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>15.9</v>
+        <v>24.1</v>
       </c>
       <c r="Q18" t="n">
         <v>22.3</v>
@@ -5323,49 +5287,45 @@
         <v>43.1</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>20.9</v>
+        <v>18.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5385,27 +5345,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 2/17, 1 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5415,67 +5375,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>34.91</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>86.62</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>97.0553</t>
+          <t>98.4627</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3741</t>
+          <t>0.3311</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1298</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3194</t>
+          <t>0.281</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>72.64</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>26.54</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>22.79</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1584</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -6447,7 +6407,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -6466,7 +6426,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>53</v>
+        <v>53.9</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6480,7 +6440,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6493,7 +6453,7 @@
         <v>43.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -6503,37 +6463,29 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>not found on RotoWire</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -7266,7 +7218,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Julio Rodriguez</t>
+          <t>Julio Rodríguez</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7291,7 +7243,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -7310,7 +7262,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>44.7</v>
+        <v>46.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7324,7 +7276,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7337,7 +7289,7 @@
         <v>43.1</v>
       </c>
       <c r="S6" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
@@ -7347,39 +7299,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7575,7 +7523,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -7594,7 +7542,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>44.6</v>
+        <v>45.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7608,7 +7556,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -7621,7 +7569,7 @@
         <v>43.1</v>
       </c>
       <c r="S7" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
@@ -7631,39 +7579,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7829,12 +7773,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>801126</t>
+          <t>663728</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brock Rodden</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7859,7 +7803,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -7878,7 +7822,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.8</v>
+        <v>45.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7892,11 +7836,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>57.3</v>
+        <v>54</v>
       </c>
       <c r="Q8" t="n">
         <v>21.2</v>
@@ -7905,52 +7849,48 @@
         <v>43.1</v>
       </c>
       <c r="S8" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T8" t="n">
         <v>75</v>
       </c>
       <c r="U8" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -7962,17 +7902,17 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -7982,7 +7922,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 2 games: 2/8, 0 HR</t>
+          <t>Last 7 games: 2/23, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -7997,67 +7937,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>98.2126</t>
+          <t>100.7149</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.4161</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.2236</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>75.06</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>53.38</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1971</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -8113,24 +8053,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>665161</t>
+          <t>801126</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jeremy Peña</t>
+          <t>Brock Rodden</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -8143,17 +8083,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -8162,7 +8102,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>43.7</v>
+        <v>44.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8176,26 +8116,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>29.3</v>
+        <v>57.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>21.2</v>
       </c>
       <c r="R9" t="n">
         <v>43.1</v>
       </c>
       <c r="S9" t="n">
-        <v>93.2</v>
+        <v>44.8</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>19.5</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -8209,7 +8149,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -8230,7 +8170,7 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -8242,17 +8182,17 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -8262,112 +8202,112 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/31, 0 HR</t>
+          <t>Last 2 games: 2/8, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>88.48</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>99.8917</t>
+          <t>98.2126</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4222</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1438</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>72.23</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1793</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -8393,12 +8333,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>670623</t>
+          <t>665161</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Isaac Paredes</t>
+          <t>Jeremy Peña</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -8423,7 +8363,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8442,7 +8382,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>43.2</v>
+        <v>43.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8460,7 +8400,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>18.7</v>
+        <v>29.3</v>
       </c>
       <c r="Q10" t="n">
         <v>41.2</v>
@@ -8469,13 +8409,13 @@
         <v>43.1</v>
       </c>
       <c r="S10" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>53.9</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -8489,7 +8429,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -8527,22 +8467,22 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Contact streak: 10/28 over last 7 games</t>
+          <t>Last 7 games: 4/31, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -8557,67 +8497,67 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>86.49</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>96.9468</t>
+          <t>99.8917</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.3772</t>
+          <t>0.4222</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1327</t>
+          <t>0.1438</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3214</t>
+          <t>0.3333</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>67.81</t>
+          <t>72.23</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>14.27</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>52.28</t>
+          <t>45.92</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>30.87</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1767</t>
+          <t>0.1793</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -8673,12 +8613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>663728</t>
+          <t>647304</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Josh Naylor</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8703,7 +8643,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -8722,7 +8662,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>42.8</v>
+        <v>43.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8736,62 +8676,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>54</v>
+        <v>24.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>21.2</v>
+        <v>22.3</v>
       </c>
       <c r="R11" t="n">
         <v>43.1</v>
       </c>
       <c r="S11" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>78.7</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8811,97 +8747,97 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/23, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.7149</t>
+          <t>99.1945</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4161</t>
+          <t>0.4068</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2236</t>
+          <t>0.1345</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>75.06</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>53.38</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1971</t>
+          <t>0.1257</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -8957,24 +8893,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>702284</t>
+          <t>670623</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cole Young</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -8987,17 +8923,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -9006,7 +8942,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>42.5</v>
+        <v>43.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9020,62 +8956,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>24.9</v>
+        <v>18.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>22.3</v>
+        <v>41.2</v>
       </c>
       <c r="R12" t="n">
         <v>43.1</v>
       </c>
       <c r="S12" t="n">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>37.8</v>
+        <v>53.9</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9095,7 +9027,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
@@ -9110,12 +9042,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 1 HR</t>
+          <t>Contact streak: 10/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -9125,97 +9057,97 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>36.63</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>88.51</t>
+          <t>86.49</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>99.0446</t>
+          <t>96.9468</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3935</t>
+          <t>0.3772</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1345</t>
+          <t>0.1327</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3166</t>
+          <t>0.3214</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>71.51</t>
+          <t>67.81</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>7.64</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>52.28</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27.22</t>
+          <t>30.87</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1767</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -9241,24 +9173,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>647304</t>
+          <t>514888</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Josh Naylor</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -9271,17 +9203,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -9290,7 +9222,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>41.1</v>
+        <v>39.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9304,62 +9236,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>24.7</v>
+        <v>14.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>22.3</v>
+        <v>41.2</v>
       </c>
       <c r="R13" t="n">
         <v>43.1</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>78.7</v>
+        <v>21.1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9379,27 +9307,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/23, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9409,97 +9337,97 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>85.24</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>99.1945</t>
+          <t>96.9722</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4068</t>
+          <t>0.3483</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1345</t>
+          <t>0.1197</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.2839</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>69.07</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1257</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -9525,24 +9453,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>514888</t>
+          <t>702284</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Cole Young</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -9555,17 +9483,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -9574,7 +9502,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9588,26 +9516,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>14.3</v>
+        <v>24.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>22.3</v>
       </c>
       <c r="R14" t="n">
         <v>43.1</v>
       </c>
       <c r="S14" t="n">
-        <v>94.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>21.1</v>
+        <v>37.8</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -9621,7 +9549,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -9659,27 +9587,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 0 HR</t>
+          <t>Last 7 games: 7/28, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -9689,97 +9617,97 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>36.63</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>85.24</t>
+          <t>88.51</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>96.9722</t>
+          <t>99.0446</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3483</t>
+          <t>0.3935</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1197</t>
+          <t>0.1345</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2839</t>
+          <t>0.3166</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>71.51</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>21.44</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>41.63</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>27.22</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -9805,12 +9733,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>621493</t>
+          <t>680977</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Brendan Donovan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9854,7 +9782,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>39.8</v>
+        <v>38.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9868,11 +9796,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>32.2</v>
+        <v>15.9</v>
       </c>
       <c r="Q15" t="n">
         <v>22.3</v>
@@ -9881,49 +9809,45 @@
         <v>43.1</v>
       </c>
       <c r="S15" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>7.9</v>
+        <v>20.9</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9943,12 +9867,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -9958,12 +9882,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/29, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9973,67 +9897,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>31.87</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>89.26</t>
+          <t>86.62</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>99.4443</t>
+          <t>97.0553</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3975</t>
+          <t>0.3741</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1546</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3379</t>
+          <t>0.3194</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>68.67</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>22.79</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -10649,12 +10573,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>680977</t>
+          <t>642215</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brendan Donovan</t>
+          <t>Weston Wilson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -10679,7 +10603,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -10698,7 +10622,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>33.7</v>
+        <v>32.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10712,11 +10636,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>15.9</v>
+        <v>24.1</v>
       </c>
       <c r="Q18" t="n">
         <v>22.3</v>
@@ -10725,49 +10649,45 @@
         <v>43.1</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>20.9</v>
+        <v>18.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10787,27 +10707,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 2/17, 1 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10817,67 +10737,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>34.91</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>86.62</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>97.0553</t>
+          <t>98.4627</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3741</t>
+          <t>0.3311</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1298</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3194</t>
+          <t>0.281</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>72.64</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>26.54</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>22.79</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1584</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-16_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-16_remaining.xlsx
@@ -1104,28 +1104,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6466,28 +6470,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/daily/hr_rankings_2026-08-16_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-16_remaining.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>66.40000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>41.2</v>
       </c>
       <c r="R2" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>53.9</v>
+        <v>53.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>22.3</v>
       </c>
       <c r="R3" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>41.2</v>
       </c>
       <c r="R4" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S4" t="n">
         <v>86.40000000000001</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46.7</v>
+        <v>46.5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>41.2</v>
       </c>
       <c r="R5" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S5" t="n">
         <v>76.2</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.5</v>
+        <v>46.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>22.3</v>
       </c>
       <c r="R6" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S6" t="n">
         <v>94.90000000000001</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>45.7</v>
+        <v>45.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>22.3</v>
       </c>
       <c r="R7" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>45.1</v>
+        <v>44.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>21.2</v>
       </c>
       <c r="R8" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S8" t="n">
         <v>64.3</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.4</v>
+        <v>44.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>21.2</v>
       </c>
       <c r="R9" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S9" t="n">
         <v>44.8</v>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>43.7</v>
+        <v>43.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>41.2</v>
       </c>
       <c r="R10" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S10" t="n">
         <v>93.2</v>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>22.3</v>
       </c>
       <c r="R11" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S11" t="n">
         <v>86.40000000000001</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>41.2</v>
       </c>
       <c r="R12" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>39.9</v>
+        <v>39.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>41.2</v>
       </c>
       <c r="R13" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S13" t="n">
         <v>94.90000000000001</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>39.8</v>
+        <v>39.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>22.3</v>
       </c>
       <c r="R14" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S14" t="n">
         <v>76.2</v>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>38.4</v>
+        <v>38.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>22.3</v>
       </c>
       <c r="R15" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S15" t="n">
         <v>93.2</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>37.6</v>
+        <v>37.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>41.2</v>
       </c>
       <c r="R16" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S16" t="n">
         <v>52.4</v>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>41.2</v>
       </c>
       <c r="R17" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S17" t="n">
         <v>64.3</v>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>32.5</v>
+        <v>32.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>22.3</v>
       </c>
       <c r="R18" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28.6</v>
+        <v>28.4</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>41.2</v>
       </c>
       <c r="R19" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>66.40000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>41.2</v>
       </c>
       <c r="R2" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>53.9</v>
+        <v>53.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>22.3</v>
       </c>
       <c r="R3" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>41.2</v>
       </c>
       <c r="R4" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S4" t="n">
         <v>86.40000000000001</v>
@@ -6925,7 +6925,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46.7</v>
+        <v>46.5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>41.2</v>
       </c>
       <c r="R5" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S5" t="n">
         <v>76.2</v>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.5</v>
+        <v>46.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>22.3</v>
       </c>
       <c r="R6" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S6" t="n">
         <v>94.90000000000001</v>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>45.7</v>
+        <v>45.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>22.3</v>
       </c>
       <c r="R7" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>45.1</v>
+        <v>44.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>21.2</v>
       </c>
       <c r="R8" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S8" t="n">
         <v>64.3</v>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.4</v>
+        <v>44.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>21.2</v>
       </c>
       <c r="R9" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S9" t="n">
         <v>44.8</v>
@@ -8325,7 +8325,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>43.7</v>
+        <v>43.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>41.2</v>
       </c>
       <c r="R10" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S10" t="n">
         <v>93.2</v>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>22.3</v>
       </c>
       <c r="R11" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S11" t="n">
         <v>86.40000000000001</v>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>41.2</v>
       </c>
       <c r="R12" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>39.9</v>
+        <v>39.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>41.2</v>
       </c>
       <c r="R13" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S13" t="n">
         <v>94.90000000000001</v>
@@ -9445,7 +9445,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>39.8</v>
+        <v>39.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>22.3</v>
       </c>
       <c r="R14" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S14" t="n">
         <v>76.2</v>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>38.4</v>
+        <v>38.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>22.3</v>
       </c>
       <c r="R15" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S15" t="n">
         <v>93.2</v>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>37.6</v>
+        <v>37.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>41.2</v>
       </c>
       <c r="R16" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S16" t="n">
         <v>52.4</v>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>41.2</v>
       </c>
       <c r="R17" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S17" t="n">
         <v>64.3</v>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>32.5</v>
+        <v>32.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>22.3</v>
       </c>
       <c r="R18" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28.6</v>
+        <v>28.4</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>41.2</v>
       </c>
       <c r="R19" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-16_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-16_remaining.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
